--- a/DrawingOrderExp2.xlsx
+++ b/DrawingOrderExp2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unigiessende-my.sharepoint.com/personal/gc2117_uni-giessen_de/Documents/Dokumente/GitHub/pep_wp4_eye_tracking/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="115" documentId="13_ncr:1_{663EEACD-2676-4766-AC79-48A4AF595AF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37E3AA48-DA36-4E88-B447-010D42446FCC}"/>
+  <xr:revisionPtr revIDLastSave="117" documentId="13_ncr:1_{663EEACD-2676-4766-AC79-48A4AF595AF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2F52DF2-A53D-40E4-9EA5-C496BFB1B6EF}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7FEFE00C-30D0-4545-AA77-F968D0DEDBC9}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1693" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1657" uniqueCount="227">
   <si>
     <t>Subject</t>
   </si>
@@ -5110,49 +5110,49 @@
         <v>82</v>
       </c>
       <c r="C54" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D54" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D54" s="1" t="s">
+      <c r="E54" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="E54" s="1" t="s">
+      <c r="F54" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="F54" s="1" t="s">
+      <c r="G54" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="G54" s="1" t="s">
+      <c r="H54" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="H54" s="1" t="s">
+      <c r="I54" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="I54" s="1" t="s">
+      <c r="J54" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="J54" s="1" t="s">
+      <c r="K54" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="K54" s="1" t="s">
+      <c r="L54" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="L54" s="1" t="s">
+      <c r="M54" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="M54" s="1" t="s">
+      <c r="N54" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="N54" s="1" t="s">
+      <c r="O54" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="O54" s="1" t="s">
+      <c r="P54" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="P54" s="1" t="s">
+      <c r="Q54" s="1" t="s">
         <v>157</v>
-      </c>
-      <c r="Q54" s="1" t="s">
-        <v>114</v>
       </c>
       <c r="R54" s="1" t="s">
         <v>114</v>
